--- a/extenbooks/S1007_extenbook.xlsx
+++ b/extenbooks/S1007_extenbook.xlsx
@@ -6103,7 +6103,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -7104,11 +7104,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7131,88 +7131,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Equity Rate vs Corporate IROP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ingested</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1007_research.json", "adequacy_report": "Technical/docs/chapters/CH10_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1007_DPR.md", "epr": "Technical/docs/series/S1007_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1007_load.py", "processor": "Technical/code/P02_processors/P02_S1007_construct.py", "validator": "Technical/code/V03_validators/V03_S1007_validate.py", "processed": "Technical/data/processed/S1007.parquet", "chopped_csv": "Technical/chopped/S1007.csv", "extenbook_xlsx": "Technical/extenbooks/S1007_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S1007-A", "S1007-B", "S1007-C"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["INTROPPRICE_iropcorp", "INTROPPRICE_iropcorpnipa", "INTROPPRICE_rreq"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1007_extenbook.xlsx
+++ b/extenbooks/S1007_extenbook.xlsx
@@ -6050,7 +6050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A119"/>
+  <dimension ref="A1:A129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6140,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>**S1007** plots three closely-related rates of return on Figure 10.7:</t>
+          <t>**S1007** plots three closely-related rates of return on Figure 10.11:</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.7, p. 469; Appendix 6.8.II.7</t>
+          <t>- Book: Shaikh (2016) Ch. 10 Fig 10.11, Appendix 10.1; Appendix 6.8.II.7</t>
         </is>
       </c>
     </row>
@@ -6707,6 +6707,68 @@
       <c r="A119" t="inlineStr">
         <is>
           <t>Informational only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>- **CD2 / CD3** — the predecessor builds of this dataset (earlier reconstructions; a "CD2 divergence" note reports how the earlier build differed, for information only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase 6** — Anu pipeline stages: Phase 5 is ingestion (building the book-period series); Phase 6 is extension (carrying the series forward with live data).</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>- **IROP / ROP** — incremental / average rate of profit (the return on newly added capital, or on the whole capital stock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>- **FRED** — the Federal Reserve Bank of St. Louis public economic-data service (source of the modern extension inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>- **BEA / NIPA** — the U.S. Bureau of Economic Analysis and its National Income and Product Accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>- **No-Lazy-Splices rule** — an internal quality rule: a derived (formula) quantity is never extended by splicing onto the published rate; the formula is recomputed from extended components so it stays analytically consistent across the book/extension boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
         </is>
       </c>
     </row>
@@ -6934,10 +6996,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -6976,61 +7038,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tolerance_pct</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
+          <t>independent_anchor_checks</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{"status": "PASS", "red_checks": [], "anchors": {"status": "GREEN", "sid": "S1007", "n_anchors": 3, "n_red": 0, "n_green": 3, "n_na": 0, "anchors": [{"anchor_id": "S1007_T102_equity_rate_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-A", "source_description": "Book Table 10.2 / Fig 10.11 (p.469): mean current-cost real equity rate of return 1947-2011 = 9.83% (decimal 0.0983; 1947 NaN, effective 1948-2011 n=64). Non-circular printed summary stat (CH10_review hand_checks_noncircular).", "status": "GREEN", "expected": 0.0983, "actual": 0.09827356, "abs_pct_diff": 0.0269, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S1007_T102_iropcorp_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-B", "source_description": "Book Table 10.2 (p.469): mean adjusted corporate real incremental rate of profit (iropcorp) 1947-2011 = 9.50% (decimal 0.0950).", "status": "GREEN", "expected": 0.095, "actual": 0.09501093, "abs_pct_diff": 0.011503, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S1007_T102_iropcorpnipa_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-C", "source_description": "Book Table 10.2 (p.469): mean NIPA corporate real incremental rate of profit (iropcorpnipa) 1947-2011 = 8.49% (decimal 0.0849).", "status": "GREEN", "expected": 0.0849, "actual": 0.08492683, "abs_pct_diff": 0.031604, "tolerance_pct": 1.0, "detail": "n=64"}]}, "splice": {"status": "NA", "sid": "S1007", "splice_year": 2012, "detail": "no subseries spans 2011-&gt;2012"}, "plausibility": {"status": "NA", "sid": "S1007", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>abs_err &gt; 0.01 (= 1 percentage point on rate_decimal)</t>
-        </is>
+          <t>tolerance_pct</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>compare_range</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1948, 2011]</t>
+          <t>abs_err &gt; 0.01 (= 1 percentage point on rate_decimal)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>n_compared</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>192</v>
+          <t>compare_range</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[1948, 2011]</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mae</t>
+          <t>n_compared</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>max_abs_err</t>
+          <t>mae</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7040,7 +7104,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>max_pct_err</t>
+          <t>max_abs_err</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -7050,46 +7114,56 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>divergence_years</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+          <t>max_pct_err</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>divergence_count</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
+          <t>divergence_years</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>per_subseries</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{"S1007-A": {"n": 64, "mae": 0.0, "max_abs_err": 0.0, "div_count": 0, "div_years_first_20": []}, "S1007-B": {"n": 64, "mae": 0.0, "max_abs_err": 0.0, "div_count": 0, "div_years_first_20": []}, "S1007-C": {"n": 64, "mae": 0.0, "max_abs_err": 0.0, "div_count": 0, "div_years_first_20": []}}</t>
-        </is>
+          <t>divergence_count</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"S1007-A": {"n": 64, "mae": 0.0, "max_abs_err": 0.0, "div_count": 0, "div_years_first_20": []}, "S1007-B": {"n": 64, "mae": 0.0, "max_abs_err": 0.0, "div_count": 0, "div_years_first_20": []}, "S1007-C": {"n": 64, "mae": 0.0, "max_abs_err": 0.0, "div_count": 0, "div_years_first_20": []}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:26:12.294959+00:00</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-02T06:18:28.179103+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1007_extenbook.xlsx
+++ b/extenbooks/S1007_extenbook.xlsx
@@ -7043,7 +7043,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"status": "PASS", "red_checks": [], "anchors": {"status": "GREEN", "sid": "S1007", "n_anchors": 3, "n_red": 0, "n_green": 3, "n_na": 0, "anchors": [{"anchor_id": "S1007_T102_equity_rate_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-A", "source_description": "Book Table 10.2 / Fig 10.11 (p.469): mean current-cost real equity rate of return 1947-2011 = 9.83% (decimal 0.0983; 1947 NaN, effective 1948-2011 n=64). Non-circular printed summary stat (CH10_review hand_checks_noncircular).", "status": "GREEN", "expected": 0.0983, "actual": 0.09827356, "abs_pct_diff": 0.0269, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S1007_T102_iropcorp_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-B", "source_description": "Book Table 10.2 (p.469): mean adjusted corporate real incremental rate of profit (iropcorp) 1947-2011 = 9.50% (decimal 0.0950).", "status": "GREEN", "expected": 0.095, "actual": 0.09501093, "abs_pct_diff": 0.011503, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S1007_T102_iropcorpnipa_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-C", "source_description": "Book Table 10.2 (p.469): mean NIPA corporate real incremental rate of profit (iropcorpnipa) 1947-2011 = 8.49% (decimal 0.0849).", "status": "GREEN", "expected": 0.0849, "actual": 0.08492683, "abs_pct_diff": 0.031604, "tolerance_pct": 1.0, "detail": "n=64"}]}, "splice": {"status": "NA", "sid": "S1007", "splice_year": 2012, "detail": "no subseries spans 2011-&gt;2012"}, "plausibility": {"status": "NA", "sid": "S1007", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+          <t>{"status": "PASS", "red_checks": [], "anchors": {"status": "GREEN", "sid": "S1007", "n_anchors": 3, "n_red": 0, "n_green": 3, "n_na": 0, "anchors": [{"anchor_id": "S1007_T102_equity_rate_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-A", "source_description": "Book Table 10.2 / Fig 10.11 (p.469): mean current-cost real equity rate of return 1947-2011 = 9.83% (decimal 0.0983; 1947 NaN, effective 1948-2011 n=64). Non-circular printed summary stat (CH10_review hand_checks_noncircular).", "status": "GREEN", "expected": 0.0983, "actual": 0.09827356, "abs_pct_diff": 0.0269, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S1007_T102_iropcorp_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-B", "source_description": "Book Table 10.2 (p.469): mean adjusted corporate real incremental rate of profit (iropcorp) 1947-2011 = 9.50% (decimal 0.0950).", "status": "GREEN", "expected": 0.095, "actual": 0.09501093, "abs_pct_diff": 0.011503, "tolerance_pct": 1.0, "detail": "n=64"}, {"anchor_id": "S1007_T102_iropcorpnipa_mean", "anchor_type": "derived_statistic", "subseries_id": "S1007-C", "source_description": "Book Table 10.2 (p.469): mean NIPA corporate real incremental rate of profit (iropcorpnipa) 1947-2011 = 8.49% (decimal 0.0849).", "status": "GREEN", "expected": 0.0849, "actual": 0.08492683, "abs_pct_diff": 0.031604, "tolerance_pct": 1.0, "detail": "n=64"}]}, "splice": {"status": "NA", "sid": "S1007", "detail": "no extension / no book+extension ranges"}, "plausibility": {"status": "NA", "sid": "S1007", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:18:28.179103+00:00</t>
+          <t>2026-07-11T03:44:22.340299+00:00</t>
         </is>
       </c>
     </row>
@@ -7178,11 +7178,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7205,6 +7205,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INTROPPRICE_rreq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Figure 10.11 (equity rate vs corporate IROP) from Shaikh Appendix 10 IntroPPrice columns; pass-through. Fixed figure reference (was 10.7, correct is 10.11).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1007_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1007_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rate_decimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
